--- a/Micropilotes/Micros.xlsx
+++ b/Micropilotes/Micros.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\CORDOBA\O-24\09666_LOTE 1 ASISTENCIA TÉCNICA PARA EL CONTR\16-2-1_E.G. PARA MEJORA DE INFRAESTRUTURAS EN L\04 INFORME\03 AN_CÁLCULOS\OTROS\Pantalla\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Desarrollo\Python\CalculoPilotes\Micropilotes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCA0518-C8E7-4A9F-B2C3-1BF0085CAB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BED9EC4-FBEE-413D-8D34-78F6414AD0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-690" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Micros Bustamante" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="48">
   <si>
     <t>E (N/mm2)</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>Diámetros perforación (mm)</t>
+  </si>
+  <si>
+    <t>La resistencia a traccion es la de compresion /1,25</t>
+  </si>
+  <si>
+    <t>La resistencia  de cortante es la de compresion /2</t>
   </si>
 </sst>
 </file>
@@ -183,8 +189,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -318,21 +324,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="88" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -341,15 +338,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="88" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
@@ -360,20 +375,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="88" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -934,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:T52"/>
+  <dimension ref="A2:T59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1066,7 +1072,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B10" t="s">
@@ -1086,7 +1092,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="15"/>
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1110,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
+      <c r="A12" s="15"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -1213,19 +1219,19 @@
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <f>C18/100^2</f>
         <v>2.2933626371205489E-4</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <f t="shared" ref="D19:F19" si="10">D18/100^2</f>
         <v>2.8274333882308137E-4</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
@@ -1358,23 +1364,23 @@
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5" t="s">
+      <c r="D30" s="14"/>
+      <c r="E30" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="14"/>
       <c r="G30" t="s">
         <v>32</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
@@ -1392,7 +1398,7 @@
       <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="13" t="s">
         <v>30</v>
       </c>
       <c r="P31" t="s">
@@ -1422,21 +1428,21 @@
       <c r="C32" s="4">
         <v>0.84</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <f>C32*$C$28</f>
         <v>0.96599999999999986</v>
       </c>
       <c r="E32" s="4">
         <v>1.52</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="7">
         <f>E32*$C$29</f>
         <v>2.4320000000000004</v>
       </c>
       <c r="G32" s="4">
         <v>5</v>
       </c>
-      <c r="O32" s="10"/>
+      <c r="O32" s="13"/>
       <c r="P32" t="s">
         <v>8</v>
       </c>
@@ -1464,21 +1470,21 @@
       <c r="C33" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="D33" s="8">
-        <f t="shared" ref="D33:F34" si="16">C33*$C$28</f>
+      <c r="D33" s="7">
+        <f t="shared" ref="D33:D34" si="16">C33*$C$28</f>
         <v>1.288</v>
       </c>
       <c r="E33" s="4">
         <v>2.19</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="7">
         <f t="shared" ref="F33:F34" si="17">E33*$C$29</f>
         <v>3.504</v>
       </c>
       <c r="G33" s="4">
         <v>3.4</v>
       </c>
-      <c r="O33" s="10"/>
+      <c r="O33" s="13"/>
       <c r="P33" t="s">
         <v>9</v>
       </c>
@@ -1506,21 +1512,21 @@
       <c r="C34" s="4">
         <v>1.5</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <f t="shared" si="16"/>
         <v>1.7249999999999999</v>
       </c>
       <c r="E34" s="4">
         <v>2.48</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="7">
         <f t="shared" si="17"/>
         <v>3.968</v>
       </c>
       <c r="G34" s="4">
         <v>6.2</v>
       </c>
-      <c r="O34" s="10" t="s">
+      <c r="O34" s="13" t="s">
         <v>31</v>
       </c>
       <c r="P34" t="s">
@@ -1544,7 +1550,7 @@
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O35" s="10"/>
+      <c r="O35" s="13"/>
       <c r="P35" t="s">
         <v>8</v>
       </c>
@@ -1567,7 +1573,7 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C36" s="4"/>
-      <c r="O36" s="10"/>
+      <c r="O36" s="13"/>
       <c r="P36" t="s">
         <v>9</v>
       </c>
@@ -1592,10 +1598,10 @@
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C38" s="7"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C39" s="7"/>
+      <c r="C39" s="6"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
@@ -1610,7 +1616,7 @@
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C40" s="7"/>
+      <c r="C40" s="6"/>
       <c r="Q40" s="4" t="s">
         <v>20</v>
       </c>
@@ -1625,16 +1631,16 @@
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C41" s="7"/>
-      <c r="Q41" s="5" t="s">
+      <c r="C41" s="6"/>
+      <c r="Q41" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O42" s="10" t="s">
+      <c r="O42" s="13" t="s">
         <v>30</v>
       </c>
       <c r="P42" t="s">
@@ -1658,7 +1664,7 @@
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O43" s="10"/>
+      <c r="O43" s="13"/>
       <c r="P43" t="s">
         <v>8</v>
       </c>
@@ -1680,7 +1686,7 @@
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O44" s="10"/>
+      <c r="O44" s="13"/>
       <c r="P44" t="s">
         <v>9</v>
       </c>
@@ -1702,7 +1708,7 @@
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O45" s="10" t="s">
+      <c r="O45" s="13" t="s">
         <v>31</v>
       </c>
       <c r="P45" t="s">
@@ -1726,7 +1732,7 @@
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O46" s="10"/>
+      <c r="O46" s="13"/>
       <c r="P46" t="s">
         <v>8</v>
       </c>
@@ -1748,7 +1754,7 @@
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O47" s="10"/>
+      <c r="O47" s="13"/>
       <c r="P47" t="s">
         <v>9</v>
       </c>
@@ -1770,15 +1776,15 @@
       </c>
     </row>
     <row r="49" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="Q49" s="5" t="s">
+      <c r="Q49" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
     </row>
     <row r="50" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P50" s="11" t="s">
+      <c r="P50" s="8" t="s">
         <v>26</v>
       </c>
       <c r="Q50">
@@ -1795,7 +1801,7 @@
       </c>
     </row>
     <row r="51" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P51" s="11" t="s">
+      <c r="P51" s="8" t="s">
         <v>27</v>
       </c>
       <c r="Q51">
@@ -1812,7 +1818,7 @@
       </c>
     </row>
     <row r="52" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P52" s="11" t="s">
+      <c r="P52" s="8" t="s">
         <v>28</v>
       </c>
       <c r="Q52">
@@ -1828,18 +1834,46 @@
         <v>37.11</v>
       </c>
     </row>
+    <row r="55" spans="16:20" x14ac:dyDescent="0.25">
+      <c r="Q55">
+        <f>Q51/Q50</f>
+        <v>1.25</v>
+      </c>
+      <c r="R55">
+        <f t="shared" ref="R55:T55" si="26">R51/R50</f>
+        <v>1.2497945768282663</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="26"/>
+        <v>1.2501062473438163</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="26"/>
+        <v>1.2499157965644998</v>
+      </c>
+    </row>
+    <row r="58" spans="16:20" x14ac:dyDescent="0.25">
+      <c r="P58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="16:20" x14ac:dyDescent="0.25">
+      <c r="P59" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="O31:O33"/>
+    <mergeCell ref="O34:O36"/>
+    <mergeCell ref="Q41:T41"/>
     <mergeCell ref="O42:O44"/>
     <mergeCell ref="O45:O47"/>
     <mergeCell ref="Q49:T49"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="O31:O33"/>
-    <mergeCell ref="O34:O36"/>
-    <mergeCell ref="Q41:T41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1981,7 +2015,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B10" t="s">
@@ -2001,7 +2035,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="15"/>
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -2019,7 +2053,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
+      <c r="A12" s="15"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -2128,19 +2162,19 @@
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <f>C18/100^2</f>
         <v>2.2933626371205489E-4</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <f t="shared" ref="D19:F19" si="10">D18/100^2</f>
         <v>2.8274333882308137E-4</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
@@ -2273,23 +2307,23 @@
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5" t="s">
+      <c r="D30" s="14"/>
+      <c r="E30" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="14"/>
       <c r="G30" t="s">
         <v>32</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
@@ -2307,7 +2341,7 @@
       <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="13" t="s">
         <v>30</v>
       </c>
       <c r="P31" t="s">
@@ -2337,21 +2371,21 @@
       <c r="C32" s="4">
         <v>0</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <f>C32*$C$28</f>
         <v>0</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="7">
         <f>E32*$C$29</f>
         <v>0</v>
       </c>
       <c r="G32" s="4">
         <v>5</v>
       </c>
-      <c r="O32" s="10"/>
+      <c r="O32" s="13"/>
       <c r="P32" t="s">
         <v>8</v>
       </c>
@@ -2379,21 +2413,21 @@
       <c r="C33" s="4">
         <v>1.8</v>
       </c>
-      <c r="D33" s="8">
-        <f t="shared" ref="D33:F34" si="16">C33*$C$28</f>
+      <c r="D33" s="7">
+        <f t="shared" ref="D33:D34" si="16">C33*$C$28</f>
         <v>2.0699999999999998</v>
       </c>
       <c r="E33" s="4">
         <v>4</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="7">
         <f t="shared" ref="F33:F34" si="17">E33*$C$29</f>
         <v>6.4</v>
       </c>
       <c r="G33" s="4">
         <v>3.4</v>
       </c>
-      <c r="O33" s="10"/>
+      <c r="O33" s="13"/>
       <c r="P33" t="s">
         <v>9</v>
       </c>
@@ -2421,21 +2455,21 @@
       <c r="C34" s="4">
         <v>0</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="7">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G34" s="4">
         <v>6.2</v>
       </c>
-      <c r="O34" s="10" t="s">
+      <c r="O34" s="13" t="s">
         <v>31</v>
       </c>
       <c r="P34" t="s">
@@ -2459,7 +2493,7 @@
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O35" s="10"/>
+      <c r="O35" s="13"/>
       <c r="P35" t="s">
         <v>8</v>
       </c>
@@ -2482,7 +2516,7 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C36" s="4"/>
-      <c r="O36" s="10"/>
+      <c r="O36" s="13"/>
       <c r="P36" t="s">
         <v>9</v>
       </c>
@@ -2507,10 +2541,10 @@
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C38" s="7"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C39" s="7"/>
+      <c r="C39" s="6"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
@@ -2525,7 +2559,7 @@
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C40" s="7"/>
+      <c r="C40" s="6"/>
       <c r="Q40" s="4" t="s">
         <v>20</v>
       </c>
@@ -2540,16 +2574,16 @@
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C41" s="7"/>
-      <c r="Q41" s="5" t="s">
+      <c r="C41" s="6"/>
+      <c r="Q41" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O42" s="10" t="s">
+      <c r="O42" s="13" t="s">
         <v>30</v>
       </c>
       <c r="P42" t="s">
@@ -2573,7 +2607,7 @@
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O43" s="10"/>
+      <c r="O43" s="13"/>
       <c r="P43" t="s">
         <v>8</v>
       </c>
@@ -2595,7 +2629,7 @@
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O44" s="10"/>
+      <c r="O44" s="13"/>
       <c r="P44" t="s">
         <v>9</v>
       </c>
@@ -2617,7 +2651,7 @@
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O45" s="10" t="s">
+      <c r="O45" s="13" t="s">
         <v>31</v>
       </c>
       <c r="P45" t="s">
@@ -2641,7 +2675,7 @@
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O46" s="10"/>
+      <c r="O46" s="13"/>
       <c r="P46" t="s">
         <v>8</v>
       </c>
@@ -2663,7 +2697,7 @@
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O47" s="10"/>
+      <c r="O47" s="13"/>
       <c r="P47" t="s">
         <v>9</v>
       </c>
@@ -2685,15 +2719,15 @@
       </c>
     </row>
     <row r="49" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="Q49" s="5" t="s">
+      <c r="Q49" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
     </row>
     <row r="50" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P50" s="11" t="s">
+      <c r="P50" s="8" t="s">
         <v>26</v>
       </c>
       <c r="Q50">
@@ -2710,7 +2744,7 @@
       </c>
     </row>
     <row r="51" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P51" s="11" t="s">
+      <c r="P51" s="8" t="s">
         <v>27</v>
       </c>
       <c r="Q51">
@@ -2727,7 +2761,7 @@
       </c>
     </row>
     <row r="52" spans="16:20" x14ac:dyDescent="0.25">
-      <c r="P52" s="11" t="s">
+      <c r="P52" s="8" t="s">
         <v>28</v>
       </c>
       <c r="Q52">
@@ -2897,7 +2931,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B10" t="s">
@@ -2917,7 +2951,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="15"/>
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -2935,7 +2969,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
+      <c r="A12" s="15"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -3044,19 +3078,19 @@
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <f>C18/100^2</f>
         <v>2.2933626371205489E-4</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <f t="shared" ref="D19:F19" si="10">D18/100^2</f>
         <v>2.8274333882308137E-4</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <f t="shared" si="10"/>
         <v>3.5814156250923637E-4</v>
       </c>
@@ -3139,12 +3173,12 @@
       <c r="C26">
         <v>1</v>
       </c>
-      <c r="Q26" s="14" t="s">
+      <c r="Q26" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
@@ -3153,16 +3187,16 @@
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="10">
         <v>125</v>
       </c>
-      <c r="R27" s="13">
+      <c r="R27" s="10">
         <v>150</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="10">
         <v>150</v>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="10">
         <v>150</v>
       </c>
     </row>
@@ -3173,16 +3207,16 @@
       <c r="C28">
         <v>1.65</v>
       </c>
-      <c r="Q28" s="12" t="s">
+      <c r="Q28" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R28" s="12" t="s">
+      <c r="R28" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="S28" s="12" t="s">
+      <c r="S28" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="T28" s="12" t="s">
+      <c r="T28" s="9" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3193,16 +3227,16 @@
       <c r="C29">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="13" t="s">
+      <c r="Q29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="R29" s="13" t="s">
+      <c r="R29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="13" t="s">
+      <c r="S29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T29" s="13" t="s">
+      <c r="T29" s="10" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3215,25 +3249,25 @@
       <c r="T30" s="24"/>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="O31" s="16" t="s">
+      <c r="O31" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="P31" s="12" t="s">
+      <c r="P31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="Q31" s="11">
         <f>D40*$C$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="R31" s="15">
+      <c r="R31" s="11">
         <f>D40*$D$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="S31" s="15">
+      <c r="S31" s="11">
         <f>D40*$E$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="T31" s="15">
+      <c r="T31" s="11">
         <f>D40*$F$6*0.1/$C$26</f>
         <v>0</v>
       </c>
@@ -3252,23 +3286,23 @@
       <c r="F32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O32" s="16"/>
-      <c r="P32" s="12" t="s">
+      <c r="O32" s="25"/>
+      <c r="P32" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="11">
         <f>D41*$C$6*0.1/$C$26</f>
         <v>4.2839899821678991</v>
       </c>
-      <c r="R32" s="15">
+      <c r="R32" s="11">
         <f>D41*$D$6*0.1/$C$26</f>
         <v>5.1407879786014794</v>
       </c>
-      <c r="S32" s="15">
+      <c r="S32" s="11">
         <f>D41*$E$6*0.1/$C$26</f>
         <v>5.1407879786014794</v>
       </c>
-      <c r="T32" s="15">
+      <c r="T32" s="11">
         <f>D41*$F$6*0.1/$C$26</f>
         <v>5.1407879786014794</v>
       </c>
@@ -3283,51 +3317,51 @@
         <v>43</v>
       </c>
       <c r="F33" s="4"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>0</v>
       </c>
       <c r="D34" s="4">
         <f>C34*10</f>
         <v>0</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6">
         <v>0</v>
       </c>
       <c r="F34" s="4">
         <f>E34*10</f>
         <v>0</v>
       </c>
-      <c r="O34" s="16" t="s">
+      <c r="O34" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="P34" s="12" t="s">
+      <c r="P34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q34" s="15">
-        <f>0.15*Q31</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="15">
-        <f>0.15*R31</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="15">
-        <f>0.15*S31</f>
-        <v>0</v>
-      </c>
-      <c r="T34" s="15">
-        <f>0.15*T31</f>
+      <c r="Q34" s="11">
+        <f t="shared" ref="Q34:T35" si="12">0.15*Q31</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -3335,65 +3369,65 @@
       <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>0.18</v>
       </c>
       <c r="D35" s="4">
         <f>C35*10</f>
         <v>1.7999999999999998</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>0.4</v>
       </c>
       <c r="F35" s="4">
         <f>E35*10</f>
         <v>4</v>
       </c>
-      <c r="O35" s="16"/>
-      <c r="P35" s="12" t="s">
+      <c r="O35" s="25"/>
+      <c r="P35" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="15">
-        <f>0.15*Q32</f>
+      <c r="Q35" s="11">
+        <f t="shared" si="12"/>
         <v>0.64259849732518481</v>
       </c>
-      <c r="R35" s="15">
-        <f>0.15*R32</f>
+      <c r="R35" s="11">
+        <f t="shared" si="12"/>
         <v>0.77111819679022187</v>
       </c>
-      <c r="S35" s="15">
-        <f>0.15*S32</f>
+      <c r="S35" s="11">
+        <f t="shared" si="12"/>
         <v>0.77111819679022187</v>
       </c>
-      <c r="T35" s="15">
-        <f>0.15*T32</f>
+      <c r="T35" s="11">
+        <f t="shared" si="12"/>
         <v>0.77111819679022187</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="C36" s="7"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
+      <c r="C36" s="6"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5" t="s">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="5"/>
+      <c r="F38" s="14"/>
       <c r="G38" t="s">
         <v>32</v>
       </c>
@@ -3415,12 +3449,12 @@
       <c r="G39" t="s">
         <v>33</v>
       </c>
-      <c r="Q39" s="14" t="s">
+      <c r="Q39" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
+      <c r="T39" s="16"/>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
@@ -3430,30 +3464,30 @@
         <f>D34</f>
         <v>0</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <f>C40/C28</f>
         <v>0</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="7">
         <f>E40/C29</f>
         <v>0</v>
       </c>
       <c r="G40" s="4">
         <v>6</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="10">
         <v>125</v>
       </c>
-      <c r="R40" s="13">
+      <c r="R40" s="10">
         <v>150</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40" s="10">
         <v>150</v>
       </c>
-      <c r="T40" s="13">
+      <c r="T40" s="10">
         <v>150</v>
       </c>
     </row>
@@ -3465,7 +3499,7 @@
         <f>D35</f>
         <v>1.7999999999999998</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <f>C41/C28</f>
         <v>1.0909090909090908</v>
       </c>
@@ -3473,222 +3507,217 @@
         <f>F35</f>
         <v>4</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="7">
         <f>E41/$C$29</f>
         <v>2.4242424242424243</v>
       </c>
       <c r="G41" s="4">
         <v>10</v>
       </c>
-      <c r="Q41" s="12" t="s">
+      <c r="Q41" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R41" s="12" t="s">
+      <c r="R41" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="S41" s="12" t="s">
+      <c r="S41" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="T41" s="12" t="s">
+      <c r="T41" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q42" s="13" t="s">
+      <c r="Q42" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="R42" s="13" t="s">
+      <c r="R42" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="S42" s="13" t="s">
+      <c r="S42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T42" s="13" t="s">
+      <c r="T42" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q43" s="25" t="s">
+      <c r="Q43" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="R43" s="25"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="25"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O44" s="18" t="s">
+      <c r="O44" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="P44" s="12" t="s">
+      <c r="P44" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q44" s="15">
+      <c r="Q44" s="11">
         <f>F40*$C$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="R44" s="15">
+      <c r="R44" s="11">
         <f>F40*$D$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="S44" s="15">
+      <c r="S44" s="11">
         <f>F40*$E$6*0.1/$C$26</f>
         <v>0</v>
       </c>
-      <c r="T44" s="15">
+      <c r="T44" s="11">
         <f>F40*$F$6*0.1/$C$26</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O45" s="19"/>
-      <c r="P45" s="12" t="s">
+      <c r="O45" s="22"/>
+      <c r="P45" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="15">
+      <c r="Q45" s="11">
         <f>F41*$C$6*0.1/$C$26</f>
         <v>9.519977738150887</v>
       </c>
-      <c r="R45" s="15">
+      <c r="R45" s="11">
         <f>F41*$D$6*0.1/$C$26</f>
         <v>11.423973285781067</v>
       </c>
-      <c r="S45" s="15">
+      <c r="S45" s="11">
         <f>F41*$E$6*0.1/$C$26</f>
         <v>11.423973285781067</v>
       </c>
-      <c r="T45" s="15">
+      <c r="T45" s="11">
         <f>F41*$F$6*0.1/$C$26</f>
         <v>11.423973285781067</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O46" s="20"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
+      <c r="O46" s="23"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O47" s="18" t="s">
+      <c r="O47" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="P47" s="12" t="s">
+      <c r="P47" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="Q47" s="15">
-        <f>0.15*Q44</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="15">
-        <f>0.15*R44</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="15">
-        <f>0.15*S44</f>
-        <v>0</v>
-      </c>
-      <c r="T47" s="15">
-        <f>0.15*T44</f>
+      <c r="Q47" s="11">
+        <f t="shared" ref="Q47:T48" si="13">0.15*Q44</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="11">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O48" s="19"/>
-      <c r="P48" s="12" t="s">
+      <c r="O48" s="22"/>
+      <c r="P48" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="15">
-        <f>0.15*Q45</f>
+      <c r="Q48" s="11">
+        <f t="shared" si="13"/>
         <v>1.4279966607226331</v>
       </c>
-      <c r="R48" s="15">
-        <f>0.15*R45</f>
+      <c r="R48" s="11">
+        <f t="shared" si="13"/>
         <v>1.71359599286716</v>
       </c>
-      <c r="S48" s="15">
-        <f>0.15*S45</f>
+      <c r="S48" s="11">
+        <f t="shared" si="13"/>
         <v>1.71359599286716</v>
       </c>
-      <c r="T48" s="15">
-        <f>0.15*T45</f>
+      <c r="T48" s="11">
+        <f t="shared" si="13"/>
         <v>1.71359599286716</v>
       </c>
     </row>
     <row r="49" spans="15:20" x14ac:dyDescent="0.25">
-      <c r="O49" s="20"/>
-      <c r="P49" s="12"/>
-      <c r="Q49" s="15"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="15"/>
-      <c r="T49" s="15"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
     </row>
     <row r="51" spans="15:20" x14ac:dyDescent="0.25">
-      <c r="Q51" s="21" t="s">
+      <c r="Q51" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="R51" s="22"/>
-      <c r="S51" s="22"/>
-      <c r="T51" s="23"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="19"/>
     </row>
     <row r="52" spans="15:20" x14ac:dyDescent="0.25">
-      <c r="P52" s="17" t="s">
+      <c r="P52" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="Q52" s="12">
+      <c r="Q52" s="9">
         <v>21.36</v>
       </c>
-      <c r="R52" s="12">
+      <c r="R52" s="9">
         <v>36.51</v>
       </c>
-      <c r="S52" s="12">
+      <c r="S52" s="9">
         <v>47.06</v>
       </c>
-      <c r="T52" s="12">
+      <c r="T52" s="9">
         <v>59.38</v>
       </c>
     </row>
     <row r="53" spans="15:20" x14ac:dyDescent="0.25">
-      <c r="P53" s="17" t="s">
+      <c r="P53" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="Q53" s="12">
+      <c r="Q53" s="9">
         <v>26.7</v>
       </c>
-      <c r="R53" s="12">
+      <c r="R53" s="9">
         <v>45.63</v>
       </c>
-      <c r="S53" s="12">
+      <c r="S53" s="9">
         <v>58.83</v>
       </c>
-      <c r="T53" s="12">
+      <c r="T53" s="9">
         <v>74.22</v>
       </c>
     </row>
     <row r="54" spans="15:20" x14ac:dyDescent="0.25">
-      <c r="P54" s="17" t="s">
+      <c r="P54" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Q54" s="12">
+      <c r="Q54" s="9">
         <v>13.35</v>
       </c>
-      <c r="R54" s="12">
+      <c r="R54" s="9">
         <v>22.82</v>
       </c>
-      <c r="S54" s="12">
+      <c r="S54" s="9">
         <v>29.41</v>
       </c>
-      <c r="T54" s="12">
+      <c r="T54" s="9">
         <v>37.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="Q51:T51"/>
-    <mergeCell ref="Q43:T43"/>
-    <mergeCell ref="O44:O46"/>
-    <mergeCell ref="O47:O49"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="E38:F38"/>
@@ -3696,6 +3725,11 @@
     <mergeCell ref="O31:O33"/>
     <mergeCell ref="O34:O36"/>
     <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="Q51:T51"/>
+    <mergeCell ref="Q43:T43"/>
+    <mergeCell ref="O44:O46"/>
+    <mergeCell ref="O47:O49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
